--- a/school_surveys/032_teacher_technology_survey--school_surveys.xlsx
+++ b/school_surveys/032_teacher_technology_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'elementary_school'}</t>
+          <t>elementary_school</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Elementary School'}</t>
+          <t>Elementary School</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'desktop_computer'}</t>
+          <t>desktop_computer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Desktop Computer'}</t>
+          <t>Desktop Computer</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Smartphone'}</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'interactive_whiteboard'}</t>
+          <t>interactive_whiteboard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Interactive Whiteboard'}</t>
+          <t>Interactive Whiteboard</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'On Hold'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>survey_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'completed'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Completed'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
